--- a/backend/local_storage/default/attendance.xlsx
+++ b/backend/local_storage/default/attendance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,8 +553,78 @@
           <t>2026-08-20 10:32:13</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-20 20:32:13</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RV001</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:29:15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-21 20:29:15</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RV004</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-08-22 13:11:09</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-22 13:11:13</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
